--- a/apps/web/public/importmallar/importmall-kundpriser.xlsx
+++ b/apps/web/public/importmallar/importmall-kundpriser.xlsx
@@ -58,7 +58,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i priset — Pris × (1 − Rabatt/100) — med en varning, eftersom kundpriset lagras som nettopris. Tom cell betyder ingen rabatt.</t>
+          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i priset — Pris × (1 − Rabatt/100) — med en varning, eftersom kundpriset lagras som nettopris. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell betyder ingen rabatt.</t>
         </r>
       </text>
     </comment>
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -110,6 +110,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -121,10 +122,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1" style="4"/>
+    <col min="2" max="2" width="14" customWidth="1" style="4"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -182,66 +183,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artikelnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SB-1200</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundnummer</t>
+          <t xml:space="preserve">Artikelnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -251,19 +237,19 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Numret på en kund som redan finns i kundregistret. Samma kund och artikel får bara förekomma en gång i filen.</t>
+          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001</t>
+          <t xml:space="preserve">SB-1200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pris</t>
+          <t xml:space="preserve">Kundnummer</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -273,32 +259,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundens pris per grundenhet i SEK, decimalkomma eller punkt, aldrig negativt. Sparas med fyra decimaler som kundens artikelpris från antal 1 och ersätter ett tidigare pris på samma artikel.</t>
+          <t xml:space="preserve">Numret på en kund som redan finns i kundregistret. Samma kund och artikel får bara förekomma en gång i filen.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890,00</t>
+          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pris</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kundens pris per grundenhet i SEK, decimalkomma eller punkt, aldrig negativt. Sparas med fyra decimaler som kundens artikelpris från antal 1 och ersätter ett tidigare pris på samma artikel.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1890,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rabatt (%)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i priset — Pris × (1 − Rabatt/100) — med en varning, eftersom kundpriset lagras som nettopris. Tom cell betyder ingen rabatt.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i priset — Pris × (1 − Rabatt/100) — med en varning, eftersom kundpriset lagras som nettopris. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell betyder ingen rabatt.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>

--- a/apps/web/public/importmallar/importmall-kundpriser.xlsx
+++ b/apps/web/public/importmallar/importmall-kundpriser.xlsx
@@ -46,7 +46,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obligatorisk. Kundens pris per grundenhet i SEK, decimalkomma eller punkt, aldrig negativt. Sparas med fyra decimaler som kundens artikelpris från antal 1 och ersätter ett tidigare pris på samma artikel.</t>
+          <t xml:space="preserve">Kundens pris per grundenhet i SEK, decimalkomma eller punkt, aldrig negativt. Sparas med fyra decimaler som kundens artikelpris från antal 1 och ersätter ett tidigare pris på samma artikel. Tom cell lämnar priset orört — en rad med varken pris eller kundens artikelnummer hoppas över.</t>
         </r>
       </text>
     </comment>
@@ -59,6 +59,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i priset — Pris × (1 − Rabatt/100) — med en varning, eftersom kundpriset lagras som nettopris. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell betyder ingen rabatt.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Vad kunden kallar artikeln, max 50 tecken. Sparas på kundkortet och skrivs ut som "Ert art.nr" på offert, orderbekräftelse, plocklista, följesedel och faktura. Ersätter ett tidigare nummer för samma kund och artikel; tom cell lämnar det orört.</t>
         </r>
       </text>
     </comment>
@@ -126,6 +138,7 @@
     <col min="2" max="2" width="14" customWidth="1" style="4"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1" style="4"/>
+    <col min="5" max="5" width="25" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -147,6 +160,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rabatt (%)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kundens artikelnummer</t>
         </is>
       </c>
     </row>
@@ -276,12 +294,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundens pris per grundenhet i SEK, decimalkomma eller punkt, aldrig negativt. Sparas med fyra decimaler som kundens artikelpris från antal 1 och ersätter ett tidigare pris på samma artikel.</t>
+          <t xml:space="preserve">Kundens pris per grundenhet i SEK, decimalkomma eller punkt, aldrig negativt. Sparas med fyra decimaler som kundens artikelpris från antal 1 och ersätter ett tidigare pris på samma artikel. Tom cell lämnar priset orört — en rad med varken pris eller kundens artikelnummer hoppas över.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -309,6 +327,28 @@
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kundens artikelnummer</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vad kunden kallar artikeln, max 50 tecken. Sparas på kundkortet och skrivs ut som "Ert art.nr" på offert, orderbekräftelse, plocklista, följesedel och faktura. Ersätter ett tidigare nummer för samma kund och artikel; tom cell lämnar det orört.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KND-4711</t>
         </is>
       </c>
     </row>

--- a/apps/web/public/importmallar/importmall-kundpriser.xlsx
+++ b/apps/web/public/importmallar/importmall-kundpriser.xlsx
@@ -71,6 +71,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Vad kunden kallar artikeln, max 50 tecken. Sparas på kundkortet och skrivs ut som "Ert art.nr" på offert, orderbekräftelse, plocklista, följesedel och faktura. Ersätter ett tidigare nummer för samma kund och artikel; tom cell lämnar det orört.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Engångskostnad per orderrad i SEK, decimalkomma eller punkt, aldrig negativ — sparas på kundpriset och läggs som en egen Ställkostnad-rad på nya offert- och orderrader när en ställkostnadsartikel är vald under System → Inställningar. Kräver Pris på raden. 0 betyder inget ställpris; tom cell lämnar det orört.</t>
         </r>
       </text>
     </comment>
@@ -139,6 +151,7 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1" style="4"/>
     <col min="5" max="5" width="25" customWidth="1" style="4"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -165,6 +178,11 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kundens artikelnummer</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ställpris</t>
         </is>
       </c>
     </row>
@@ -352,6 +370,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ställpris</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engångskostnad per orderrad i SEK, decimalkomma eller punkt, aldrig negativ — sparas på kundpriset och läggs som en egen Ställkostnad-rad på nya offert- och orderrader när en ställkostnadsartikel är vald under System → Inställningar. Kräver Pris på raden. 0 betyder inget ställpris; tom cell lämnar det orört.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
